--- a/엣지코드_리스트.xlsx
+++ b/엣지코드_리스트.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15620" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -482,13 +482,21 @@
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="n">
@@ -512,7 +520,11 @@
       <c r="B8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="n">

--- a/엣지코드_리스트.xlsx
+++ b/엣지코드_리스트.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C9"/>
+  <dimension ref="B2:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="2">
@@ -484,7 +484,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -502,19 +502,31 @@
       <c r="B5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="n">
@@ -522,7 +534,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -530,7 +542,18 @@
       <c r="B9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
